--- a/Luban/Config/Datas/Levels/L24/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L24/EnemyList.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L24 W1/25; N=54; EHP=351.648000; normal:17x27,normal:18x27</t>
+          <t>L24 W1/25; N=54; EHP=947.205853; normal:17x27,normal:18x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L24 W2/25; N=60; EHP=409.122912; normal:17x30,normal:18x30</t>
+          <t>L24 W2/25; N=60; EHP=1102.021387; normal:17x30,normal:18x30 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>10019654,10019656,10048853,10019654,10019656,10048853,10019654,10019656,10048854,10019654,10019656,10048855,10019654,10019656,10048855,10019654,10019656,10048856,10019654,10019656,10048856,10019654,10019656,10048857,10019654,10019656,10019654,10019656,10019654,10019656,10019654,10019656,10019654,10019656,10019654,10019656,10019654,10019656,10019654,10019656,10019654,10019656,10019654,10019656,10019654,10019654,10019655,10019655,10019655,10019655,10019655,10019655,10019655,10019655,10019655,10019655,10019655,10019655,10019655,10019655,10019655,10019655,10019655,10019655,10019655,10019655</t>
+          <t>10019654,10019656,10019654,10019656,10019654,10019656,10019654,10019656,10019654,10019656,10019654,10019656,10019654,10019656,10019654,10019656,10019654,10019656,10019654,10019656,10019654,10019656,10019654,10019656,10019654,10019656,10019654,10019656,10019654,10019656,10019654,10019656,10019654,10019656,10019654,10019656,10019654,10019654,10019655,10019655,10019655,10019655,10019655,10019655,10019655,10019655,10019655,10019655,10019655,10019655,10019655,10019655,10019655,10019655,10019655,10019655,10019655,10019655,10019654,10019654,10019654,10019654,10019654,10019654,10019654,10019654</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L24 W3/25; N=66; EHP=497.871053; air:2x2,air:11x1,air:12x2,air:13x2,air:14x1,normal:17x20,normal:18x20,swarm:84x18</t>
+          <t>L24 W3/25; N=66; EHP=1447.779081; normal:17x28,normal:18x20,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>10019657,10019659,10048858,10019657,10019659,10048858,10019657,10019659,10048859,10019657,10019659,10048859,10019657,10019659,10048860,10019657,10019659,10048861,10019657,10019659,10048861,10019657,10019659,10048862,10019657,10019659,10048862,10019657,10019659,10019657,10019659,10019657,10019659,10019657,10019659,10019657,10019659,10019657,10019659,10019657,10019659,10019657,10019659,10019657,10019659,10019657,10019659,10019657,10019659,10019657,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658</t>
+          <t>10019657,10019659,10019657,10019659,10019657,10019659,10019657,10019659,10019657,10019659,10019657,10019659,10019657,10019659,10019657,10019659,10019657,10019659,10019657,10019659,10019657,10019659,10019657,10019659,10019657,10019659,10019657,10019659,10019657,10019659,10019657,10019659,10019657,10019659,10019657,10019659,10019657,10019659,10019657,10019659,10019657,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658,10019658</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L24 W4/25; N=72; EHP=625.417690; air:2x2,air:11x2,air:12x1,air:13x2,air:14x2,normal:17x21,normal:18x22,swarm:84x20</t>
+          <t>L24 W4/25; N=72; EHP=1823.504028; normal:17x21,normal:18x31,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>10019660,10019663,10048863,10019662,10019660,10019663,10048864,10019662,10019660,10019663,10048864,10019662,10019660,10019663,10048865,10019662,10019660,10019663,10048865,10019664,10019660,10019663,10048866,10019664,10019660,10019663,10048866,10019664,10019660,10019663,10048867,10019664,10019660,10019663,10048867,10019665,10019660,10019663,10019665,10019660,10019663,10019665,10019660,10019663,10019660,10019663,10019660,10019663,10019660,10019663,10019660,10019663,10019660,10019663,10019660,10019663,10019660,10019663,10019661,10019663,10019661,10019663,10019661,10019661,10019661,10019661,10019661,10019661,10019661,10019661,10019661,10019661,10019661,10019661,10019661,10019661,10019661,10019661</t>
+          <t>10019660,10048863,10048863,10019662,10019660,10048864,10048864,10019662,10019660,10048864,10048864,10019662,10019660,10048865,10048865,10019662,10019660,10048865,10048865,10019664,10019660,10048866,10048866,10019664,10019660,10048866,10048866,10019664,10019660,10048867,10048867,10019664,10019660,10048867,10048867,10019665,10019660,10019663,10019665,10019660,10019663,10019665,10019660,10019663,10019660,10019663,10019660,10019663,10019660,10019663,10019660,10019663,10019660,10019663,10019660,10019663,10019660,10019663,10019661,10019663,10019661,10019663,10019661,10019661,10019661,10019661,10019661,10019661,10019661,10019661,10019661,10019661,10019661,10019661,10019661,10019661,10019661,10019661</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L24 W5/25; N=78; EHP=1168.000000; air:2x1,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x19,normal:18x18,medium:83x4,swarm:84x21,medium:108x4,medium:123x3</t>
+          <t>L24 W5/25; N=78; EHP=3184.724125; air:2x2,air:11x4,air:12x4,air:13x4,air:14x4,medium:83x4,medium:108x4,medium:123x3,normal:17x19,normal:18x18,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>10019669,10019675,10019671,10048868,10019674,10019669,10019675,10019671,10048868,10019674,10019669,10019675,10019672,10019666,10019674,10019669,10019675,10019672,10019666,10019674,10019669,10019675,10019672,10048869,10019677,10019669,10019675,10019673,10048869,10019677,10019669,10019675,10019673,10019667,10019677,10019669,10019675,10019673,10019667,10019677,10019669,10019675,10019676,10019668,10019678,10019669,10019675,10019676,10019668,10019678,10019669,10019675,10019678,10019669,10019675,10019678,10019669,10019675,10019669,10019675,10019670,10019675,10019670,10019675,10019670,10019675,10019670,10019675,10019670,10019675,10019670,10019675,10019670,10019675,10019670,10019675,10019670,10019675,10019670,10019670,10019670,10019670,10019670,10019670</t>
+          <t>10019669,10048868,10019671,10048868,10019674,10019669,10048868,10019671,10048868,10019674,10019669,10019666,10019672,10019666,10019674,10019669,10019666,10019672,10019666,10019674,10019669,10048869,10019672,10048869,10019677,10019669,10048869,10019673,10048869,10019677,10019669,10019667,10019673,10019667,10019677,10019669,10019667,10019673,10019667,10019677,10019669,10019668,10019676,10019668,10019678,10019669,10019668,10019676,10019668,10019678,10019669,10019675,10019678,10019669,10019675,10019678,10019669,10019675,10019669,10019675,10019670,10019675,10019670,10019675,10019670,10019675,10019670,10019675,10019670,10019675,10019670,10019675,10019670,10019675,10019670,10019675,10019670,10019675,10019670,10019670,10019670,10019670,10019670,10019670</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L24 W6/25; N=84; EHP=1192.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x14,normal:18x15,fast:30x2,fast:58x3,fast:64x3,medium:83x4,swarm:84x23,fast:98x2,medium:108x4,medium:123x4</t>
+          <t>L24 W6/25; N=84; EHP=3252.304195; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x2,fast:58x3,fast:64x3,fast:98x2,medium:83x4,medium:108x4,medium:123x4,normal:17x14,normal:18x15,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>10019682,10019688,10019684,10048870,10019687,10019682,10019688,10019684,10048870,10019687,10019682,10019688,10019684,10019679,10019687,10019682,10019688,10019685,10019679,10019687,10019682,10019688,10019685,10048871,10019690,10019682,10019688,10019686,10048871,10019690,10019682,10019688,10019686,10019680,10019690,10019682,10019688,10019686,10019680,10019690,10019682,10019688,10019689,10019681,10019691,10019682,10019688,10019689,10019681,10019691,10019682,10019688,10019681,10019691,10019682,10019688,10019691,10019682,10019688,10019691,10019682,10019688,10019682,10019688,10019682,10019688,10019683,10019688,10019683,10019688,10019683,10019688,10019683,10019688,10019683,10019688,10019683,10019688,10019683,10019688,10019683,10019688,10019683,10019688,10019683,10019683,10019683,10019683,10019683,10019683</t>
+          <t>10019682,10048870,10019684,10048870,10019687,10019682,10048870,10019684,10048870,10019687,10019682,10019679,10019684,10019679,10019687,10019682,10019679,10019685,10019679,10019687,10019682,10048871,10019685,10048871,10019690,10019682,10048871,10019686,10048871,10019690,10019682,10019680,10019686,10019680,10019690,10019682,10019680,10019686,10019680,10019690,10019682,10019681,10019689,10019681,10019691,10019682,10019681,10019689,10019681,10019691,10019682,10019681,10019681,10019691,10019682,10019688,10019691,10019682,10019688,10019691,10019682,10019688,10019682,10019688,10019682,10019688,10019683,10019688,10019683,10019688,10019683,10019688,10019683,10019688,10019683,10019688,10019683,10019688,10019683,10019688,10019683,10019688,10019683,10019688,10019683,10019683,10019683,10019683,10019683,10019683</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L24 W7/25; N=90; EHP=1337.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x3,normal:17x16,normal:18x15,fast:30x3,fast:58x2,fast:64x3,medium:83x4,swarm:84x25,fast:98x2,medium:108x4,medium:123x5</t>
+          <t>L24 W7/25; N=90; EHP=3649.213329; air:2x4,air:11x4,air:12x4,air:13x4,air:14x6,fast:30x3,fast:58x2,fast:64x3,fast:98x2,medium:83x4,medium:108x4,medium:123x5,normal:17x16,normal:18x15,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>10019695,10019701,10019697,10048872,10019700,10019695,10019701,10019697,10048872,10019700,10019695,10019701,10019697,10048872,10019700,10019695,10019701,10019698,10019692,10019700,10019695,10019701,10019698,10019692,10019700,10019695,10019701,10019698,10048873,10019703,10019695,10019701,10019699,10048873,10019703,10019695,10019701,10019699,10048873,10019703,10019695,10019701,10019702,10019693,10019703,10019695,10019701,10019702,10019693,10019703,10019695,10019701,10019702,10019694,10019704,10019695,10019701,10019694,10019704,10019695,10019701,10019704,10019695,10019701,10019704,10019695,10019701,10019695,10019701,10019696,10019701,10019696,10019701,10019696,10019701,10019696,10019701,10019696,10019701,10019696,10019701,10019696,10019701,10019696,10019701,10019696,10019701,10019696,10019701,10019696,10019696,10019696,10019696,10019696,10019696,10019696</t>
+          <t>10019695,10048872,10019697,10048872,10019700,10019695,10048872,10019697,10048872,10019700,10019695,10048872,10019697,10048872,10019700,10019695,10019692,10019698,10019692,10019700,10019695,10019692,10019698,10019692,10019700,10019695,10048873,10019698,10048873,10019703,10019695,10048873,10019699,10048873,10019703,10019695,10048873,10019699,10048873,10019703,10019695,10019693,10019702,10019693,10019703,10019695,10019693,10019702,10019693,10019703,10019695,10019694,10019702,10019694,10019704,10019695,10019694,10019694,10019704,10019695,10019701,10019704,10019695,10019701,10019704,10019695,10019701,10019695,10019701,10019696,10019701,10019696,10019701,10019696,10019701,10019696,10019701,10019696,10019701,10019696,10019701,10019696,10019701,10019696,10019701,10019696,10019701,10019696,10019701,10019696,10019696,10019696,10019696,10019696,10019696,10019696</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L24 W8/25; N=96; EHP=1717.000000; air:2x3,air:11x2,air:12x3,air:13x2,air:14x2,normal:17x16,normal:18x17,fast:30x3,fast:58x3,fast:64x2,medium:83x5,swarm:84x26,fast:98x3,medium:108x5,medium:123x4</t>
+          <t>L24 W8/25; N=96; EHP=4687.690963; air:2x6,air:11x4,air:12x6,air:13x4,air:14x4,fast:30x3,fast:58x3,fast:64x2,fast:98x3,medium:83x5,medium:108x5,medium:123x4,normal:17x16,normal:18x17,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>10019708,10019714,10019710,10048874,10019713,10019708,10019714,10019710,10048874,10019713,10019708,10019714,10019710,10048874,10019713,10019708,10019714,10019711,10019705,10019713,10019708,10019714,10019711,10019705,10019713,10019708,10019714,10019711,10048875,10019716,10019708,10019714,10019712,10048875,10019716,10019708,10019714,10019712,10019706,10019716,10019708,10019714,10019712,10019706,10019716,10019708,10019714,10019715,10019706,10019716,10019708,10019714,10019715,10019707,10019717,10019708,10019714,10019715,10019707,10019717,10019708,10019714,10019717,10019708,10019714,10019717,10019708,10019714,10019717,10019708,10019714,10019708,10019714,10019708,10019714,10019709,10019714,10019709,10019714,10019709,10019714,10019709,10019714,10019709,10019714,10019709,10019714,10019709,10019714,10019709,10019714,10019709,10019714,10019709,10019714,10019709,10019709,10019709,10019709,10019709,10019709,10019709</t>
+          <t>10019708,10048874,10019710,10048874,10019713,10019708,10048874,10019710,10048874,10019713,10019708,10048874,10019710,10048874,10019713,10019708,10019705,10019711,10019705,10019713,10019708,10019705,10019711,10019705,10019713,10019708,10048875,10019711,10048875,10019716,10019708,10048875,10019712,10048875,10019716,10019708,10019706,10019712,10019706,10019716,10019708,10019706,10019712,10019706,10019716,10019708,10019706,10019715,10019706,10019716,10019708,10019707,10019715,10019707,10019717,10019708,10019707,10019715,10019707,10019717,10019708,10019714,10019717,10019708,10019714,10019717,10019708,10019714,10019717,10019708,10019714,10019708,10019714,10019708,10019714,10019709,10019714,10019709,10019714,10019709,10019714,10019709,10019714,10019709,10019714,10019709,10019714,10019709,10019714,10019709,10019714,10019709,10019714,10019709,10019714,10019709,10019709,10019709,10019709,10019709,10019709,10019709</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L24 W9/25; N=102; EHP=2191.000000; air:2x3,air:11x2,air:12x2,air:13x3,air:14x2,normal:17x18,normal:18x17,fast:30x3,fast:58x3,fast:64x3,medium:83x5,swarm:84x28,fast:98x3,medium:108x5,medium:123x5</t>
+          <t>L24 W9/25; N=102; EHP=5976.821389; air:2x6,air:11x4,air:12x4,air:13x6,air:14x4,fast:30x3,fast:58x3,fast:64x3,fast:98x3,medium:83x5,medium:108x5,medium:123x5,normal:17x18,normal:18x17,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>10019721,10019727,10019723,10048876,10019726,10019721,10019727,10019723,10048876,10019726,10019721,10019727,10019723,10019718,10019726,10019721,10019727,10019724,10019718,10019726,10019721,10019727,10019724,10019718,10019726,10019721,10019727,10019724,10048877,10019729,10019721,10019727,10019725,10048877,10019729,10019721,10019727,10019725,10019719,10019729,10019721,10019727,10019725,10019719,10019729,10019721,10019727,10019728,10019719,10019729,10019721,10019727,10019728,10019720,10019730,10019721,10019727,10019728,10019720,10019730,10019721,10019727,10019720,10019730,10019721,10019727,10019730,10019721,10019727,10019730,10019721,10019727,10019730,10019721,10019727,10019721,10019727,10019722,10019727,10019722,10019727,10019722,10019727,10019722,10019727,10019722,10019727,10019722,10019727,10019722,10019727,10019722,10019727,10019722,10019727,10019722,10019727,10019722,10019727,10019722,10019727,10019722,10019722,10019722,10019722,10019722,10019722,10019722</t>
+          <t>10019721,10048876,10019723,10048876,10019726,10019721,10048876,10019723,10048876,10019726,10019721,10019718,10019723,10019718,10019726,10019721,10019718,10019724,10019718,10019726,10019721,10019718,10019724,10019718,10019726,10019721,10048877,10019724,10048877,10019729,10019721,10048877,10019725,10048877,10019729,10019721,10019719,10019725,10019719,10019729,10019721,10019719,10019725,10019719,10019729,10019721,10019719,10019728,10019719,10019729,10019721,10019720,10019728,10019720,10019730,10019721,10019720,10019728,10019720,10019730,10019721,10019720,10019720,10019730,10019721,10019727,10019730,10019721,10019727,10019730,10019721,10019727,10019730,10019721,10019727,10019721,10019727,10019722,10019727,10019722,10019727,10019722,10019727,10019722,10019727,10019722,10019727,10019722,10019727,10019722,10019727,10019722,10019727,10019722,10019727,10019722,10019727,10019722,10019727,10019722,10019727,10019722,10019722,10019722,10019722,10019722,10019722,10019722</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L24 W10/25; N=108; EHP=4038.000000; air:2x2,air:11x3,air:12x2,air:13x3,air:14x3,normal:17x18,normal:18x19,fast:30x3,fast:58x3,fast:64x3,medium:83x5,swarm:84x30,fast:98x3,medium:108x5,medium:123x6</t>
+          <t>L24 W10/25; N=108; EHP=11018.588121; air:2x4,air:11x6,air:12x4,air:13x6,air:14x6,fast:30x3,fast:58x3,fast:64x3,fast:98x3,medium:83x5,medium:108x5,medium:123x6,normal:17x18,normal:18x19,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>10019731,10019741,10019733,10048878,10019740,10019734,10019731,10019741,10019733,10048878,10019740,10019734,10019731,10019741,10019733,10048878,10019740,10019735,10019731,10019741,10019736,10048879,10019740,10019735,10019731,10019741,10019736,10048879,10019740,10019738,10019731,10019741,10019736,10048879,10019740,10019739,10019731,10019741,10019737,10048880,10019744,10045255,10019731,10019741,10019737,10048880,10019744,10045256,10019731,10019741,10019737,10048880,10019744,10019742,10019731,10019741,10019737,10048881,10019744,10019746,10019731,10019741,10019743,10048881,10019744,10019746,10019731,10019741,10019743,10048882,10019744,10019731,10019741,10019743,10048882,10019745,10019731,10019741,10048882,10019745,10019732,10019741,10019745,10019732,10019741,10019745,10019732,10019741,10019745,10019732,10019741,10019732,10019741,10019732,10019741,10019732,10019741,10019732,10019741,10019732,10019741,10019732,10019741,10019732,10019741,10019732,10019741,10019732,10019741,10019732,10019741,10019741,10019741,10019741</t>
+          <t>10019731,10048878,10019733,10048878,10019740,10019734,10019731,10048878,10019733,10048878,10019740,10019734,10019731,10048878,10019733,10048878,10019740,10019735,10019731,10048879,10019736,10048879,10019740,10019735,10019731,10048879,10019736,10048879,10019740,10019738,10019731,10048879,10019736,10048879,10019740,10019739,10019731,10048880,10019737,10048880,10019744,10045255,10019731,10048880,10019737,10048880,10019744,10045256,10019731,10048880,10019737,10048880,10019744,10019742,10019731,10048881,10019737,10048881,10019744,10019746,10019731,10048881,10019743,10048881,10019744,10019746,10019731,10048882,10019743,10048882,10019744,10019731,10048882,10019743,10048882,10019745,10019731,10048882,10048882,10019745,10019732,10019741,10019745,10019732,10019741,10019745,10019732,10019741,10019745,10019732,10019741,10019732,10019741,10019732,10019741,10019732,10019741,10019732,10019741,10019732,10019741,10019732,10019741,10019732,10019741,10019732,10019741,10019732,10019741,10019732,10019741,10019741,10019741,10019741</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L24 W11/25; N=114; EHP=4119.000000; air:2x3,air:11x3,air:12x3,air:13x2,air:14x3,normal:17x14,normal:18x14,fast:30x3,heavy:31x2,heavy:40x2,fast:58x3,fast:64x4,heavy:67x1,heavy:70x1,heavy:80x1,medium:83x6,swarm:84x31,heavy:86x1,heavy:88x1,fast:98x3,medium:108x6,medium:123x5,heavy:127x2</t>
+          <t>L24 W11/25; N=114; EHP=11225.987910; air:2x6,air:11x6,air:12x6,air:13x4,air:14x6,fast:30x3,fast:58x3,fast:64x4,fast:98x3,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x2,medium:83x6,medium:108x6,medium:123x5,normal:17x14,normal:18x14,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>10019750,10019760,10019752,10048883,10019759,10045257,10019750,10019760,10019752,10048883,10019759,10019753,10019750,10019760,10019752,10048883,10019759,10019753,10019750,10019760,10019752,10019747,10019759,10019756,10019750,10019760,10019754,10019747,10019759,10019756,10019750,10019760,10019754,10048884,10019759,10019757,10019750,10019760,10019754,10048884,10019763,10019757,10019750,10019760,10019755,10048884,10019763,10019758,10019750,10019760,10019755,10019748,10019763,10045258,10019750,10019760,10019755,10019748,10019763,10019761,10019750,10019760,10019762,10019748,10019763,10019765,10019750,10019760,10019762,10019749,10019763,10019765,10019750,10019760,10019762,10019749,10019764,10019750,10019760,10019762,10019749,10019764,10019751,10019760,10019764,10019751,10019760,10019764,10019751,10019760,10019764,10019751,10019760,10019764,10019751,10019760,10019751,10019760,10019751,10019760,10019751,10019760,10019751,10019760,10019751,10019760,10019751,10019760,10019751,10019760,10019751,10019760,10019751,10019760,10019751,10019760,10019760,10019760,10019760,10019760</t>
+          <t>10019750,10048883,10019752,10048883,10019759,10045257,10019750,10048883,10019752,10048883,10019759,10019753,10019750,10048883,10019752,10048883,10019759,10019753,10019750,10019747,10019752,10019747,10019759,10019756,10019750,10019747,10019754,10019747,10019759,10019756,10019750,10048884,10019754,10048884,10019759,10019757,10019750,10048884,10019754,10048884,10019763,10019757,10019750,10048884,10019755,10048884,10019763,10019758,10019750,10019748,10019755,10019748,10019763,10045258,10019750,10019748,10019755,10019748,10019763,10019761,10019750,10019748,10019762,10019748,10019763,10019765,10019750,10019749,10019762,10019749,10019763,10019765,10019750,10019749,10019762,10019749,10019764,10019750,10019749,10019762,10019749,10019764,10019751,10019760,10019764,10019751,10019760,10019764,10019751,10019760,10019764,10019751,10019760,10019764,10019751,10019760,10019751,10019760,10019751,10019760,10019751,10019760,10019751,10019760,10019751,10019760,10019751,10019760,10019751,10019760,10019751,10019760,10019751,10019760,10019751,10019760,10019760,10019760,10019760,10019760</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L24 W12/25; N=120; EHP=4262.000000; air:2x3,air:11x2,air:12x3,air:13x3,air:14x3,normal:17x14,normal:18x15,fast:30x4,heavy:31x1,heavy:40x2,fast:58x3,fast:64x3,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x6,swarm:84x33,heavy:86x1,heavy:88x1,fast:98x4,medium:108x6,medium:123x6,heavy:127x2</t>
+          <t>L24 W12/25; N=120; EHP=11608.118770; air:2x6,air:11x4,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x3,fast:64x3,fast:98x4,heavy:31x1,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x2,medium:83x6,medium:108x6,medium:123x6,normal:17x14,normal:18x15,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>10019769,10019778,10019771,10048885,10019777,10045259,10019769,10019778,10019771,10048885,10019777,10045260,10019769,10019778,10019771,10048885,10019777,10019774,10019769,10019778,10019772,10019766,10019777,10019774,10019769,10019778,10019772,10019766,10019777,10019775,10019769,10019778,10019772,10019766,10019777,10019775,10019769,10019778,10019772,10048886,10019782,10019776,10019769,10019778,10019773,10048886,10019782,10019779,10019769,10019778,10019773,10048886,10019782,10019780,10019769,10019778,10019773,10019767,10019782,10019780,10019769,10019778,10019773,10019767,10019782,10019784,10019769,10019778,10019781,10019767,10019782,10019784,10019769,10019778,10019781,10019768,10019783,10019769,10019778,10019781,10019768,10019783,10019769,10019778,10019781,10019768,10019783,10019769,10019778,10019783,10019770,10019778,10019783,10019770,10019778,10019783,10019770,10019778,10019770,10019778,10019770,10019778,10019770,10019778,10019770,10019778,10019770,10019778,10019770,10019778,10019770,10019778,10019770,10019778,10019770,10019778,10019770,10019778,10019770,10019778,10019770,10019778,10019778,10019778,10019778,10019778</t>
+          <t>10019769,10048885,10019771,10048885,10019777,10045259,10019769,10048885,10019771,10048885,10019777,10045260,10019769,10048885,10019771,10048885,10019777,10019774,10019769,10019766,10019772,10019766,10019777,10019774,10019769,10019766,10019772,10019766,10019777,10019775,10019769,10019766,10019772,10019766,10019777,10019775,10019769,10048886,10019772,10048886,10019782,10019776,10019769,10048886,10019773,10048886,10019782,10019779,10019769,10048886,10019773,10048886,10019782,10019780,10019769,10019767,10019773,10019767,10019782,10019780,10019769,10019767,10019773,10019767,10019782,10019784,10019769,10019767,10019781,10019767,10019782,10019784,10019769,10019768,10019781,10019768,10019783,10019769,10019768,10019781,10019768,10019783,10019769,10019768,10019781,10019768,10019783,10019769,10019778,10019783,10019770,10019778,10019783,10019770,10019778,10019783,10019770,10019778,10019770,10019778,10019770,10019778,10019770,10019778,10019770,10019778,10019770,10019778,10019770,10019778,10019770,10019778,10019770,10019778,10019770,10019778,10019770,10019778,10019770,10019778,10019770,10019778,10019778,10019778,10019778,10019778</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L24 W13/25; N=126; EHP=5198.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x16,normal:18x15,fast:30x3,heavy:31x1,heavy:40x1,fast:58x4,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x6,swarm:84x35,heavy:86x1,heavy:88x2,fast:98x4,medium:108x6,medium:123x6,heavy:127x2</t>
+          <t>L24 W13/25; N=126; EHP=14162.678229; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x3,fast:58x4,fast:64x4,fast:98x4,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x2,heavy:127x2,medium:83x6,medium:108x6,medium:123x6,normal:17x16,normal:18x15,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>10019788,10019798,10019790,10048887,10019797,10019791,10019788,10019798,10019790,10048887,10019797,10045261,10019788,10019798,10019790,10048887,10019797,10019794,10019788,10019798,10019790,10048887,10019797,10019794,10019788,10019798,10019792,10019785,10019797,10019795,10019788,10019798,10019792,10019785,10019797,10019795,10019788,10019798,10019792,10019785,10019802,10019796,10019788,10019798,10019792,10048888,10019802,10019796,10019788,10019798,10019793,10048888,10019802,10019799,10019788,10019798,10019793,10048888,10019802,10019799,10019788,10019798,10019793,10019786,10019802,10019800,10019788,10019798,10019793,10019786,10019802,10019800,10019788,10019798,10019801,10019786,10019802,10045262,10019788,10019798,10019801,10019787,10019803,10019788,10019798,10019801,10019787,10019803,10019788,10019798,10019787,10019803,10019789,10019798,10019803,10019789,10019798,10019803,10019789,10019798,10019803,10019789,10019798,10019789,10019798,10019789,10019798,10019789,10019798,10019789,10019798,10019789,10019798,10019789,10019798,10019789,10019798,10019789,10019798,10019789,10019798,10019789,10019798,10019789,10019798,10019789,10019798,10019789,10019798,10019798,10019798,10019798</t>
+          <t>10019788,10048887,10019790,10048887,10019797,10019791,10019788,10048887,10019790,10048887,10019797,10045261,10019788,10048887,10019790,10048887,10019797,10019794,10019788,10048887,10019790,10048887,10019797,10019794,10019788,10019785,10019792,10019785,10019797,10019795,10019788,10019785,10019792,10019785,10019797,10019795,10019788,10019785,10019792,10019785,10019802,10019796,10019788,10048888,10019792,10048888,10019802,10019796,10019788,10048888,10019793,10048888,10019802,10019799,10019788,10048888,10019793,10048888,10019802,10019799,10019788,10019786,10019793,10019786,10019802,10019800,10019788,10019786,10019793,10019786,10019802,10019800,10019788,10019786,10019801,10019786,10019802,10045262,10019788,10019787,10019801,10019787,10019803,10019788,10019787,10019801,10019787,10019803,10019788,10019787,10019787,10019803,10019789,10019798,10019803,10019789,10019798,10019803,10019789,10019798,10019803,10019789,10019798,10019789,10019798,10019789,10019798,10019789,10019798,10019789,10019798,10019789,10019798,10019789,10019798,10019789,10019798,10019789,10019798,10019789,10019798,10019789,10019798,10019789,10019798,10019789,10019798,10019789,10019798,10019798,10019798,10019798</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L24 W14/25; N=132; EHP=6270.000000; air:2x4,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x16,normal:18x17,fast:30x4,heavy:31x1,heavy:40x1,fast:58x4,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x6,swarm:84x36,heavy:86x2,heavy:88x2,fast:98x3,medium:108x7,medium:123x6,heavy:127x1</t>
+          <t>L24 W14/25; N=132; EHP=17085.877684; air:2x8,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x4,fast:64x4,fast:98x3,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x6,medium:108x7,medium:123x6,normal:17x16,normal:18x17,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>10019807,10019818,10019809,10048889,10019817,10019810,10019814,10019807,10019818,10019809,10048889,10019817,10019810,10019807,10019818,10019809,10048889,10019817,10019811,10019807,10019818,10019809,10019804,10019817,10019815,10019807,10019818,10019812,10019804,10019817,10019815,10019807,10019818,10019812,10019804,10019817,10045263,10019807,10019818,10019812,10019804,10019817,10019816,10019807,10019818,10019812,10048890,10019822,10019816,10019807,10019818,10019813,10048890,10019822,10019819,10019807,10019818,10019813,10048890,10019822,10019819,10019807,10019818,10019813,10019805,10019822,10019820,10019807,10019818,10019813,10019805,10019822,10019820,10019807,10019818,10019821,10019805,10019822,10045264,10019807,10019818,10019821,10019805,10019823,10019807,10019818,10019821,10019806,10019823,10019807,10019818,10019821,10019806,10019823,10019807,10019818,10019806,10019823,10019808,10019818,10019823,10019808,10019818,10019823,10019808,10019818,10019823,10019808,10019818,10019808,10019818,10019808,10019818,10019808,10019818,10019808,10019818,10019808,10019818,10019808,10019818,10019808,10019818,10019808,10019818,10019808,10019818,10019808,10019818,10019808,10019818,10019808,10019818,10019818,10019818,10019818,10019818,10019818</t>
+          <t>10019807,10048889,10019809,10048889,10019817,10019810,10019814,10019807,10048889,10019809,10048889,10019817,10019810,10019807,10048889,10019809,10048889,10019817,10019811,10019807,10019804,10019809,10019804,10019817,10019815,10019807,10019804,10019812,10019804,10019817,10019815,10019807,10019804,10019812,10019804,10019817,10045263,10019807,10019804,10019812,10019804,10019817,10019816,10019807,10048890,10019812,10048890,10019822,10019816,10019807,10048890,10019813,10048890,10019822,10019819,10019807,10048890,10019813,10048890,10019822,10019819,10019807,10019805,10019813,10019805,10019822,10019820,10019807,10019805,10019813,10019805,10019822,10019820,10019807,10019805,10019821,10019805,10019822,10045264,10019807,10019805,10019821,10019805,10019823,10019807,10019806,10019821,10019806,10019823,10019807,10019806,10019821,10019806,10019823,10019807,10019806,10019806,10019823,10019808,10019818,10019823,10019808,10019818,10019823,10019808,10019818,10019823,10019808,10019818,10019808,10019818,10019808,10019818,10019808,10019818,10019808,10019818,10019808,10019818,10019808,10019818,10019808,10019818,10019808,10019818,10019808,10019818,10019808,10019818,10019808,10019818,10019808,10019818,10019818,10019818,10019818,10019818,10019818</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L24 W15/25; N=138; EHP=10943.000000; air:2x3,air:11x4,air:12x3,air:13x4,air:14x3,normal:17x17,normal:18x16,fast:30x4,heavy:31x2,heavy:40x1,fast:58x4,fast:64x4,elite:67x1,heavy:67x2,heavy:70x1,heavy:80x2,medium:83x7,swarm:84x38,heavy:86x2,heavy:88x2,fast:98x4,medium:108x6,medium:123x7,heavy:127x1</t>
+          <t>L24 W15/25; N=138; EHP=29818.672514; air:2x6,air:11x8,air:12x6,air:13x8,air:14x6,elite:67x1,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x2,heavy:40x1,heavy:67x2,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x7,medium:108x6,medium:123x7,normal:17x17,normal:18x16,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>10019824,10019834,10019826,10048891,10019833,10019827,10019824,10019834,10019826,10048891,10019833,10019827,10019824,10019834,10019826,10048891,10019833,10019828,10019824,10019834,10019826,10048892,10019833,10019828,10019824,10019834,10019826,10048892,10019833,10045265,10019824,10019834,10019829,10048892,10019833,10019831,10019824,10019834,10019829,10048892,10019833,10019832,10019824,10019834,10019829,10048893,10019838,10019832,10019824,10019834,10019829,10048893,10019838,10019835,10019824,10019834,10019830,10048893,10019838,10019835,10019824,10019834,10019830,10048894,10019838,10019836,10019824,10019834,10019830,10048894,10019838,10019836,10019824,10019834,10019830,10048894,10019838,10019840,10019824,10019834,10019837,10048895,10019838,10019840,10019824,10019834,10019837,10048895,10019839,10019824,10019834,10019837,10048895,10019839,10019824,10019834,10019837,10048895,10019839,10019825,10019834,10019839,10019825,10019834,10019839,10019825,10019834,10019839,10019825,10019834,10019839,10019825,10019834,10019825,10019834,10019825,10019834,10019825,10019834,10019825,10019834,10019825,10019834,10019825,10019834,10019825,10019834,10019825,10019834,10019825,10019834,10019825,10019834,10019825,10019834,10019825,10019834,10019825,10019834,10019834,10019834,10019834,10019834,10019834</t>
+          <t>10019824,10048891,10019826,10048891,10019833,10019827,10019824,10048891,10019826,10048891,10019833,10019827,10019824,10048891,10019826,10048891,10019833,10019828,10019824,10048892,10019826,10048892,10019833,10019828,10019824,10048892,10019826,10048892,10019833,10045265,10019824,10048892,10019829,10048892,10019833,10019831,10019824,10048892,10019829,10048892,10019833,10019832,10019824,10048893,10019829,10048893,10019838,10019832,10019824,10048893,10019829,10048893,10019838,10019835,10019824,10048893,10019830,10048893,10019838,10019835,10019824,10048894,10019830,10048894,10019838,10019836,10019824,10048894,10019830,10048894,10019838,10019836,10019824,10048894,10019830,10048894,10019838,10019840,10019824,10048895,10019837,10048895,10019838,10019840,10019824,10048895,10019837,10048895,10019839,10019824,10048895,10019837,10048895,10019839,10019824,10048895,10019837,10048895,10019839,10019825,10019834,10019839,10019825,10019834,10019839,10019825,10019834,10019839,10019825,10019834,10019839,10019825,10019834,10019825,10019834,10019825,10019834,10019825,10019834,10019825,10019834,10019825,10019834,10019825,10019834,10019825,10019834,10019825,10019834,10019825,10019834,10019825,10019834,10019825,10019834,10019825,10019834,10019825,10019834,10019834,10019834,10019834,10019834,10019834</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L24 W16/25; N=144; EHP=11162.000000; air:2x3,air:11x4,air:12x3,air:13x3,air:14x4,normal:17x17,normal:18x18,fast:30x5,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x7,swarm:84x40,heavy:86x2,heavy:88x2,fast:98x4,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L24 W16/25; N=144; EHP=30407.840169; air:2x6,air:11x8,air:12x6,air:13x6,air:14x8,fast:30x5,fast:58x4,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x7,medium:108x7,medium:123x7,normal:17x17,normal:18x18,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>10019844,10019855,10019846,10048896,10019854,10019847,10019844,10019855,10019846,10048896,10019854,10019847,10019844,10019855,10019846,10048896,10019854,10019848,10019844,10019855,10019846,10048896,10019854,10019848,10019844,10019855,10019849,10019841,10019854,10019851,10019844,10019855,10019849,10019841,10019854,10019851,10019844,10019855,10019849,10019841,10019854,10019852,10019844,10019855,10019849,10048897,10019858,10019852,10019844,10019855,10019849,10048897,10019858,10019853,10019844,10019855,10019850,10048897,10019858,10019853,10019844,10019855,10019850,10048897,10019858,10019856,10019844,10019855,10019850,10019842,10019858,10019856,10019844,10019855,10019850,10019842,10019858,10045266,10019844,10019855,10019857,10019842,10019858,10019860,10019844,10019855,10019857,10019843,10019858,10019860,10019844,10019855,10019857,10019843,10019859,10019844,10019855,10019857,10019843,10019859,10019844,10019855,10019857,10019843,10019859,10019845,10019855,10019859,10019845,10019855,10019859,10019845,10019855,10019859,10019845,10019855,10019859,10019845,10019855,10019845,10019855,10019845,10019855,10019845,10019855,10019845,10019855,10019845,10019855,10019845,10019855,10019845,10019855,10019845,10019855,10019845,10019855,10019845,10019855,10019845,10019855,10019845,10019855,10019855,10019855,10019855,10019855,10019855,10019855,10019855</t>
+          <t>10019844,10048896,10019846,10048896,10019854,10019847,10019844,10048896,10019846,10048896,10019854,10019847,10019844,10048896,10019846,10048896,10019854,10019848,10019844,10048896,10019846,10048896,10019854,10019848,10019844,10019841,10019849,10019841,10019854,10019851,10019844,10019841,10019849,10019841,10019854,10019851,10019844,10019841,10019849,10019841,10019854,10019852,10019844,10048897,10019849,10048897,10019858,10019852,10019844,10048897,10019849,10048897,10019858,10019853,10019844,10048897,10019850,10048897,10019858,10019853,10019844,10048897,10019850,10048897,10019858,10019856,10019844,10019842,10019850,10019842,10019858,10019856,10019844,10019842,10019850,10019842,10019858,10045266,10019844,10019842,10019857,10019842,10019858,10019860,10019844,10019843,10019857,10019843,10019858,10019860,10019844,10019843,10019857,10019843,10019859,10019844,10019843,10019857,10019843,10019859,10019844,10019843,10019857,10019843,10019859,10019845,10019855,10019859,10019845,10019855,10019859,10019845,10019855,10019859,10019845,10019855,10019859,10019845,10019855,10019845,10019855,10019845,10019855,10019845,10019855,10019845,10019855,10019845,10019855,10019845,10019855,10019845,10019855,10019845,10019855,10019845,10019855,10019845,10019855,10019845,10019855,10019845,10019855,10019855,10019855,10019855,10019855,10019855,10019855,10019855</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L24 W17/25; N=150; EHP=11386.000000; air:2x4,air:11x3,air:12x4,air:13x3,air:14x4,normal:17x18,normal:18x17,fast:30x4,heavy:31x2,heavy:40x2,fast:58x5,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x42,heavy:86x2,heavy:88x1,fast:98x5,medium:108x8,medium:123x7,heavy:127x2</t>
+          <t>L24 W17/25; N=150; EHP=31023.202495; air:2x8,air:11x6,air:12x8,air:13x6,air:14x8,fast:30x4,fast:58x5,fast:64x4,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x1,heavy:127x2,medium:83x7,medium:108x8,medium:123x7,normal:17x18,normal:18x17,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>10019864,10019874,10019866,10048898,10019873,10019867,10019864,10019874,10019866,10048898,10019873,10019867,10019864,10019874,10019866,10048898,10019873,10019868,10019864,10019874,10019866,10048898,10019873,10019868,10019864,10019874,10019869,10019861,10019873,10019871,10019864,10019874,10019869,10019861,10019873,10019871,10019864,10019874,10019869,10019861,10019873,10019872,10019864,10019874,10019869,10019861,10019873,10019872,10019864,10019874,10019869,10048899,10019878,10045267,10019864,10019874,10019870,10048899,10019878,10019875,10019864,10019874,10019870,10048899,10019878,10019875,10019864,10019874,10019870,10048899,10019878,10019876,10019864,10019874,10019870,10019862,10019878,10019876,10019864,10019874,10019870,10019862,10019878,10019880,10019864,10019874,10019877,10019862,10019878,10019880,10019864,10019874,10019877,10019862,10019879,10019864,10019874,10019877,10019863,10019879,10019864,10019874,10019877,10019863,10019879,10019864,10019874,10019863,10019879,10019865,10019874,10019879,10019865,10019874,10019879,10019865,10019874,10019879,10019865,10019874,10019879,10019865,10019874,10019865,10019874,10019865,10019874,10019865,10019874,10019865,10019874,10019865,10019874,10019865,10019874,10019865,10019874,10019865,10019874,10019865,10019874,10019865,10019874,10019865,10019874,10019865,10019874,10019865,10019874,10019865,10019874,10019874,10019874,10019874,10019874,10019874</t>
+          <t>10019864,10048898,10019866,10048898,10019873,10019867,10019864,10048898,10019866,10048898,10019873,10019867,10019864,10048898,10019866,10048898,10019873,10019868,10019864,10048898,10019866,10048898,10019873,10019868,10019864,10019861,10019869,10019861,10019873,10019871,10019864,10019861,10019869,10019861,10019873,10019871,10019864,10019861,10019869,10019861,10019873,10019872,10019864,10019861,10019869,10019861,10019873,10019872,10019864,10048899,10019869,10048899,10019878,10045267,10019864,10048899,10019870,10048899,10019878,10019875,10019864,10048899,10019870,10048899,10019878,10019875,10019864,10048899,10019870,10048899,10019878,10019876,10019864,10019862,10019870,10019862,10019878,10019876,10019864,10019862,10019870,10019862,10019878,10019880,10019864,10019862,10019877,10019862,10019878,10019880,10019864,10019862,10019877,10019862,10019879,10019864,10019863,10019877,10019863,10019879,10019864,10019863,10019877,10019863,10019879,10019864,10019863,10019863,10019879,10019865,10019874,10019879,10019865,10019874,10019879,10019865,10019874,10019879,10019865,10019874,10019879,10019865,10019874,10019865,10019874,10019865,10019874,10019865,10019874,10019865,10019874,10019865,10019874,10019865,10019874,10019865,10019874,10019865,10019874,10019865,10019874,10019865,10019874,10019865,10019874,10019865,10019874,10019865,10019874,10019865,10019874,10019874,10019874,10019874,10019874,10019874</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L24 W18/25; N=156; EHP=12163.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x3,normal:17x19,normal:18x19,fast:30x4,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x8,swarm:84x43,heavy:86x2,heavy:88x2,fast:98x4,medium:108x7,medium:123x8,heavy:127x2</t>
+          <t>L24 W18/25; N=156; EHP=33146.980789; air:2x8,air:11x8,air:12x8,air:13x8,air:14x6,fast:30x4,fast:58x5,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x7,medium:123x8,normal:17x19,normal:18x19,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>10019884,10019895,10019886,10048900,10019894,10019887,10019884,10019895,10019886,10048900,10019894,10019887,10019884,10019895,10019886,10048900,10019894,10019888,10019884,10019895,10019886,10048900,10019894,10019888,10019884,10019895,10019886,10019881,10019894,10019891,10019884,10019895,10019889,10019881,10019894,10019891,10019884,10019895,10019889,10019881,10019894,10019892,10019884,10019895,10019889,10019881,10019894,10019892,10019884,10019895,10019889,10048901,10019898,10019893,10019884,10019895,10019890,10048901,10019898,10019893,10019884,10019895,10019890,10048901,10019898,10045268,10019884,10019895,10019890,10019882,10019898,10045268,10019884,10019895,10019890,10019882,10019898,10019896,10019884,10019895,10019890,10019882,10019898,10019896,10019884,10019895,10019897,10019882,10019898,10019900,10019884,10019895,10019897,10019883,10019898,10019900,10019884,10019895,10019897,10019883,10019899,10019884,10019895,10019897,10019883,10019899,10019884,10019895,10019897,10019883,10019899,10019884,10019895,10019899,10019885,10019895,10019899,10019885,10019895,10019899,10019885,10019895,10019899,10019885,10019895,10019899,10019885,10019895,10019885,10019895,10019885,10019895,10019885,10019895,10019885,10019895,10019885,10019895,10019885,10019895,10019885,10019895,10019885,10019895,10019885,10019895,10019885,10019895,10019885,10019895,10019885,10019895,10019885,10019895,10019885,10019895,10019895,10019895,10019895,10019895,10019895,10019895</t>
+          <t>10019884,10048900,10019886,10048900,10019894,10019887,10019884,10048900,10019886,10048900,10019894,10019887,10019884,10048900,10019886,10048900,10019894,10019888,10019884,10048900,10019886,10048900,10019894,10019888,10019884,10019881,10019886,10019881,10019894,10019891,10019884,10019881,10019889,10019881,10019894,10019891,10019884,10019881,10019889,10019881,10019894,10019892,10019884,10019881,10019889,10019881,10019894,10019892,10019884,10048901,10019889,10048901,10019898,10019893,10019884,10048901,10019890,10048901,10019898,10019893,10019884,10048901,10019890,10048901,10019898,10045268,10019884,10019882,10019890,10019882,10019898,10045268,10019884,10019882,10019890,10019882,10019898,10019896,10019884,10019882,10019890,10019882,10019898,10019896,10019884,10019882,10019897,10019882,10019898,10019900,10019884,10019883,10019897,10019883,10019898,10019900,10019884,10019883,10019897,10019883,10019899,10019884,10019883,10019897,10019883,10019899,10019884,10019883,10019897,10019883,10019899,10019884,10019895,10019899,10019885,10019895,10019899,10019885,10019895,10019899,10019885,10019895,10019899,10019885,10019895,10019899,10019885,10019895,10019885,10019895,10019885,10019895,10019885,10019895,10019885,10019895,10019885,10019895,10019885,10019895,10019885,10019895,10019885,10019895,10019885,10019895,10019885,10019895,10019885,10019895,10019885,10019895,10019885,10019895,10019885,10019895,10019895,10019895,10019895,10019895,10019895,10019895</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L24 W19/25; N=162; EHP=14089.000000; air:2x4,air:11x4,air:12x3,air:13x4,air:14x4,normal:17x20,normal:18x19,fast:30x5,heavy:31x2,heavy:40x2,fast:58x4,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x45,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L24 W19/25; N=162; EHP=38377.190447; air:2x8,air:11x8,air:12x6,air:13x8,air:14x8,fast:30x5,fast:58x4,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x8,normal:17x20,normal:18x19,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>10019904,10019915,10019906,10048902,10019914,10045269,10019910,10019904,10019915,10019906,10048902,10019914,10045269,10019904,10019915,10019906,10048902,10019914,10019907,10019904,10019915,10019906,10048902,10019914,10019907,10019904,10019915,10019906,10019901,10019914,10019911,10019904,10019915,10019908,10019901,10019914,10019911,10019904,10019915,10019908,10019901,10019914,10019912,10019904,10019915,10019908,10019901,10019914,10019912,10019904,10019915,10019908,10048903,10019919,10019913,10019904,10019915,10019908,10048903,10019919,10019913,10019904,10019915,10019909,10048903,10019919,10019916,10019904,10019915,10019909,10048903,10019919,10019916,10019904,10019915,10019909,10019902,10019919,10019917,10019904,10019915,10019909,10019902,10019919,10019917,10019904,10019915,10019909,10019902,10019919,10019921,10019904,10019915,10019918,10019902,10019919,10019921,10019904,10019915,10019918,10019903,10019919,10019904,10019915,10019918,10019903,10019920,10019904,10019915,10019918,10019903,10019920,10019905,10019915,10019918,10019903,10019920,10019905,10019915,10019920,10019905,10019915,10019920,10019905,10019915,10019920,10019905,10019915,10019920,10019905,10019915,10019920,10019905,10019915,10019905,10019915,10019905,10019915,10019905,10019915,10019905,10019915,10019905,10019915,10019905,10019915,10019905,10019915,10019905,10019915,10019905,10019915,10019905,10019915,10019905,10019915,10019905,10019915,10019905,10019915,10019915,10019915,10019915,10019915,10019915,10019915,10019915,10019915</t>
+          <t>10019904,10048902,10019906,10048902,10019914,10045269,10019910,10019904,10048902,10019906,10048902,10019914,10045269,10019904,10048902,10019906,10048902,10019914,10019907,10019904,10048902,10019906,10048902,10019914,10019907,10019904,10019901,10019906,10019901,10019914,10019911,10019904,10019901,10019908,10019901,10019914,10019911,10019904,10019901,10019908,10019901,10019914,10019912,10019904,10019901,10019908,10019901,10019914,10019912,10019904,10048903,10019908,10048903,10019919,10019913,10019904,10048903,10019908,10048903,10019919,10019913,10019904,10048903,10019909,10048903,10019919,10019916,10019904,10048903,10019909,10048903,10019919,10019916,10019904,10019902,10019909,10019902,10019919,10019917,10019904,10019902,10019909,10019902,10019919,10019917,10019904,10019902,10019909,10019902,10019919,10019921,10019904,10019902,10019918,10019902,10019919,10019921,10019904,10019903,10019918,10019903,10019919,10019904,10019903,10019918,10019903,10019920,10019904,10019903,10019918,10019903,10019920,10019905,10019903,10019918,10019903,10019920,10019905,10019915,10019920,10019905,10019915,10019920,10019905,10019915,10019920,10019905,10019915,10019920,10019905,10019915,10019920,10019905,10019915,10019905,10019915,10019905,10019915,10019905,10019915,10019905,10019915,10019905,10019915,10019905,10019915,10019905,10019915,10019905,10019915,10019905,10019915,10019905,10019915,10019905,10019915,10019905,10019915,10019905,10019915,10019915,10019915,10019915,10019915,10019915,10019915,10019915,10019915</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L24 W20/25; N=168; EHP=23648.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x19,normal:18x20,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,elite:67x1,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x47,heavy:86x2,heavy:88x2,fast:98x5,medium:108x9,medium:123x8,heavy:127x2</t>
+          <t>L24 W20/25; N=168; EHP=64414.224947; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,elite:67x1,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x9,medium:123x8,normal:17x19,normal:18x20,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>10019925,10019936,10019927,10048904,10019935,10019928,10019925,10019936,10019927,10048904,10019935,10019928,10019925,10019936,10019927,10048904,10019935,10019929,10019925,10019936,10019927,10048904,10019935,10019929,10019925,10019936,10019927,10019922,10019935,10019932,10019925,10019936,10019930,10019922,10019935,10019932,10019925,10019936,10019930,10019922,10019935,10019933,10019925,10019936,10019930,10019922,10019935,10019933,10019925,10019936,10019930,10019922,10019935,10019934,10019925,10019936,10019930,10048905,10019940,10019934,10019925,10019936,10019931,10048905,10019940,10019937,10019925,10019936,10019931,10048905,10019940,10019937,10019925,10019936,10019931,10048905,10019940,10019938,10019925,10019936,10019931,10019923,10019940,10019938,10019925,10019936,10019931,10019923,10019940,10019942,10019925,10019936,10019939,10019923,10019940,10019942,10019925,10019936,10019939,10019923,10019940,10019942,10019925,10019936,10019939,10019924,10019941,10019925,10019936,10019939,10019924,10019941,10019925,10019936,10019939,10019924,10019941,10019925,10019936,10019924,10019941,10019926,10019936,10019941,10019926,10019936,10019941,10019926,10019936,10019941,10019926,10019936,10019941,10019926,10019936,10019941,10019926,10019936,10019926,10019936,10019926,10019936,10019926,10019936,10019926,10019936,10019926,10019936,10019926,10019936,10019926,10019936,10019926,10019936,10019926,10019936,10019926,10019936,10019926,10019936,10019926,10019936,10019926,10019936,10019926,10019936,10019926,10019936,10019936,10019936,10019936,10019936,10019936,10019936</t>
+          <t>10019925,10048904,10019927,10048904,10019935,10019928,10019925,10048904,10019927,10048904,10019935,10019928,10019925,10048904,10019927,10048904,10019935,10019929,10019925,10048904,10019927,10048904,10019935,10019929,10019925,10019922,10019927,10019922,10019935,10019932,10019925,10019922,10019930,10019922,10019935,10019932,10019925,10019922,10019930,10019922,10019935,10019933,10019925,10019922,10019930,10019922,10019935,10019933,10019925,10019922,10019930,10019922,10019935,10019934,10019925,10048905,10019930,10048905,10019940,10019934,10019925,10048905,10019931,10048905,10019940,10019937,10019925,10048905,10019931,10048905,10019940,10019937,10019925,10048905,10019931,10048905,10019940,10019938,10019925,10019923,10019931,10019923,10019940,10019938,10019925,10019923,10019931,10019923,10019940,10019942,10019925,10019923,10019939,10019923,10019940,10019942,10019925,10019923,10019939,10019923,10019940,10019942,10019925,10019924,10019939,10019924,10019941,10019925,10019924,10019939,10019924,10019941,10019925,10019924,10019939,10019924,10019941,10019925,10019924,10019924,10019941,10019926,10019936,10019941,10019926,10019936,10019941,10019926,10019936,10019941,10019926,10019936,10019941,10019926,10019936,10019941,10019926,10019936,10019926,10019936,10019926,10019936,10019926,10019936,10019926,10019936,10019926,10019936,10019926,10019936,10019926,10019936,10019926,10019936,10019926,10019936,10019926,10019936,10019926,10019936,10019926,10019936,10019926,10019936,10019926,10019936,10019926,10019936,10019936,10019936,10019936,10019936,10019936,10019936</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L24 W21/25; N=174; EHP=24121.000000; air:2x4,air:11x5,air:12x4,air:13x4,air:14x4,normal:17x21,normal:18x21,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x48,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x9,heavy:127x3</t>
+          <t>L24 W21/25; N=174; EHP=65725.580248; air:2x8,air:11x10,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x3,medium:83x9,medium:108x8,medium:123x9,normal:17x21,normal:18x21,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>10019946,10019957,10019948,10048906,10019956,10019949,10019946,10019957,10019948,10048906,10019956,10019949,10019946,10019957,10019948,10048906,10019956,10019950,10019946,10019957,10019948,10048906,10019956,10019950,10019946,10019957,10019948,10019943,10019956,10019953,10019946,10019957,10019951,10019943,10019956,10019953,10019946,10019957,10019951,10019943,10019956,10019953,10019946,10019957,10019951,10019943,10019956,10019954,10019946,10019957,10019951,10048907,10019956,10019954,10019946,10019957,10019951,10048907,10019961,10019954,10019946,10019957,10019951,10048907,10019961,10019955,10019946,10019957,10019952,10048907,10019961,10019955,10019946,10019957,10019952,10048907,10019961,10019958,10019946,10019957,10019952,10019944,10019961,10019958,10019946,10019957,10019952,10019944,10019961,10019959,10019946,10019957,10019952,10019944,10019961,10019959,10019946,10019957,10019960,10019944,10019961,10019963,10019946,10019957,10019960,10019945,10019961,10019963,10019946,10019957,10019960,10019945,10019962,10019946,10019957,10019960,10019945,10019962,10019946,10019957,10019960,10019945,10019962,10019947,10019957,10019945,10019962,10019947,10019957,10019962,10019947,10019957,10019962,10019947,10019957,10019962,10019947,10019957,10019962,10019947,10019957,10019962,10019947,10019957,10019947,10019957,10019947,10019957,10019947,10019957,10019947,10019957,10019947,10019957,10019947,10019957,10019947,10019957,10019947,10019957,10019947,10019957,10019947,10019957,10019947,10019957,10019947,10019957,10019947,10019957,10019947,10019957,10019957,10019957,10019957,10019957,10019957,10019957,10019957,10019957</t>
+          <t>10019946,10048906,10019948,10048906,10019956,10019949,10019946,10048906,10019948,10048906,10019956,10019949,10019946,10048906,10019948,10048906,10019956,10019950,10019946,10048906,10019948,10048906,10019956,10019950,10019946,10019943,10019948,10019943,10019956,10019953,10019946,10019943,10019951,10019943,10019956,10019953,10019946,10019943,10019951,10019943,10019956,10019953,10019946,10019943,10019951,10019943,10019956,10019954,10019946,10048907,10019951,10048907,10019956,10019954,10019946,10048907,10019951,10048907,10019961,10019954,10019946,10048907,10019951,10048907,10019961,10019955,10019946,10048907,10019952,10048907,10019961,10019955,10019946,10048907,10019952,10048907,10019961,10019958,10019946,10019944,10019952,10019944,10019961,10019958,10019946,10019944,10019952,10019944,10019961,10019959,10019946,10019944,10019952,10019944,10019961,10019959,10019946,10019944,10019960,10019944,10019961,10019963,10019946,10019945,10019960,10019945,10019961,10019963,10019946,10019945,10019960,10019945,10019962,10019946,10019945,10019960,10019945,10019962,10019946,10019945,10019960,10019945,10019962,10019947,10019945,10019945,10019962,10019947,10019957,10019962,10019947,10019957,10019962,10019947,10019957,10019962,10019947,10019957,10019962,10019947,10019957,10019962,10019947,10019957,10019947,10019957,10019947,10019957,10019947,10019957,10019947,10019957,10019947,10019957,10019947,10019957,10019947,10019957,10019947,10019957,10019947,10019957,10019947,10019957,10019947,10019957,10019947,10019957,10019947,10019957,10019947,10019957,10019957,10019957,10019957,10019957,10019957,10019957,10019957,10019957</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L24 W22/25; N=180; EHP=24604.000000; air:2x4,air:11x4,air:12x5,air:13x4,air:14x5,normal:17x21,normal:18x21,fast:30x5,heavy:31x2,heavy:40x2,fast:58x6,fast:64x5,heavy:67x3,heavy:70x3,heavy:80x2,medium:83x9,swarm:84x50,heavy:86x2,heavy:88x2,fast:98x5,medium:108x9,medium:123x9,heavy:127x2</t>
+          <t>L24 W22/25; N=180; EHP=67050.387447; air:2x8,air:11x8,air:12x10,air:13x8,air:14x10,fast:30x5,fast:58x6,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x3,heavy:70x3,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x9,medium:108x9,medium:123x9,normal:17x21,normal:18x21,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>10019967,10019978,10019969,10048908,10019977,10019970,10019967,10019978,10019969,10048908,10019977,10019970,10019967,10019978,10019969,10048908,10019977,10019971,10019967,10019978,10019969,10048908,10019977,10019971,10019967,10019978,10019969,10048908,10019977,10019974,10019967,10019978,10019969,10019964,10019977,10019974,10019967,10019978,10019972,10019964,10019977,10019974,10019967,10019978,10019972,10019964,10019977,10019975,10019967,10019978,10019972,10019964,10019977,10019975,10019967,10019978,10019972,10048909,10019982,10019976,10019967,10019978,10019972,10048909,10019982,10019976,10019967,10019978,10019973,10048909,10019982,10019979,10019967,10019978,10019973,10048909,10019982,10019979,10019967,10019978,10019973,10048909,10019982,10019980,10019967,10019978,10019973,10019965,10019982,10019980,10019967,10019978,10019973,10019965,10019982,10019980,10019967,10019978,10019973,10019965,10019982,10019984,10019967,10019978,10019981,10019965,10019982,10019984,10019967,10019978,10019981,10019966,10019983,10019967,10019978,10019981,10019966,10019983,10019967,10019978,10019981,10019966,10019983,10019967,10019978,10019981,10019966,10019983,10019967,10019978,10019983,10019968,10019978,10019983,10019968,10019978,10019983,10019968,10019978,10019983,10019968,10019978,10019983,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019978,10019978,10019978,10019978,10019978,10019978,10019978</t>
+          <t>10019967,10048908,10019969,10048908,10019977,10019970,10019967,10048908,10019969,10048908,10019977,10019970,10019967,10048908,10019969,10048908,10019977,10019971,10019967,10048908,10019969,10048908,10019977,10019971,10019967,10048908,10019969,10048908,10019977,10019974,10019967,10019964,10019969,10019964,10019977,10019974,10019967,10019964,10019972,10019964,10019977,10019974,10019967,10019964,10019972,10019964,10019977,10019975,10019967,10019964,10019972,10019964,10019977,10019975,10019967,10048909,10019972,10048909,10019982,10019976,10019967,10048909,10019972,10048909,10019982,10019976,10019967,10048909,10019973,10048909,10019982,10019979,10019967,10048909,10019973,10048909,10019982,10019979,10019967,10048909,10019973,10048909,10019982,10019980,10019967,10019965,10019973,10019965,10019982,10019980,10019967,10019965,10019973,10019965,10019982,10019980,10019967,10019965,10019973,10019965,10019982,10019984,10019967,10019965,10019981,10019965,10019982,10019984,10019967,10019966,10019981,10019966,10019983,10019967,10019966,10019981,10019966,10019983,10019967,10019966,10019981,10019966,10019983,10019967,10019966,10019981,10019966,10019983,10019967,10019978,10019983,10019968,10019978,10019983,10019968,10019978,10019983,10019968,10019978,10019983,10019968,10019978,10019983,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019968,10019978,10019978,10019978,10019978,10019978,10019978,10019978,10019978</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L24 W23/25; N=186; EHP=25097.000000; air:2x5,air:11x4,air:12x5,air:13x4,air:14x4,normal:17x23,normal:18x22,fast:30x6,heavy:31x2,heavy:40x2,fast:58x5,fast:64x6,heavy:67x3,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x52,heavy:86x2,heavy:88x3,fast:98x5,medium:108x9,medium:123x9,heavy:127x2</t>
+          <t>L24 W23/25; N=186; EHP=68372.754049; air:2x10,air:11x8,air:12x10,air:13x8,air:14x8,fast:30x6,fast:58x5,fast:64x6,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x3,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x3,heavy:127x2,medium:83x9,medium:108x9,medium:123x9,normal:17x23,normal:18x22,swarm:84x30 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>10019988,10019999,10019990,10048910,10019998,10019991,10019988,10019999,10019990,10048910,10019998,10019991,10019988,10019999,10019990,10048910,10019998,10019992,10019988,10019999,10019990,10048910,10019998,10019992,10019988,10019999,10019990,10048910,10019998,10019995,10019988,10019999,10019990,10019985,10019998,10019995,10019988,10019999,10019993,10019985,10019998,10019996,10019988,10019999,10019993,10019985,10019998,10019996,10019988,10019999,10019993,10019985,10019998,10019997,10019988,10019999,10019993,10019985,10019998,10019997,10019988,10019999,10019993,10048911,10020003,10019997,10019988,10019999,10019993,10048911,10020003,10020000,10019988,10019999,10019994,10048911,10020003,10020000,10019988,10019999,10019994,10048911,10020003,10020000,10019988,10019999,10019994,10019986,10020003,10020001,10019988,10019999,10019994,10019986,10020003,10020001,10019988,10019999,10019994,10019986,10020003,10020001,10019988,10019999,10020002,10019986,10020003,10020005,10019988,10019999,10020002,10019986,10020003,10020005,10019988,10019999,10020002,10019987,10020004,10019988,10019999,10020002,10019987,10020004,10019988,10019999,10020002,10019987,10020004,10019988,10019999,10020002,10019987,10020004,10019989,10019999,10020004,10019989,10019999,10020004,10019989,10019999,10020004,10019989,10019999,10020004,10019989,10019999,10020004,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019999,10019999,10019999,10019999,10019999,10019999,10019999</t>
+          <t>10019988,10048910,10019990,10048910,10019998,10019991,10019988,10048910,10019990,10048910,10019998,10019991,10019988,10048910,10019990,10048910,10019998,10019992,10019988,10048910,10019990,10048910,10019998,10019992,10019988,10048910,10019990,10048910,10019998,10019995,10019988,10019985,10019990,10019985,10019998,10019995,10019988,10019985,10019993,10019985,10019998,10019996,10019988,10019985,10019993,10019985,10019998,10019996,10019988,10019985,10019993,10019985,10019998,10019997,10019988,10019985,10019993,10019985,10019998,10019997,10019988,10048911,10019993,10048911,10020003,10019997,10019988,10048911,10019993,10048911,10020003,10020000,10019988,10048911,10019994,10048911,10020003,10020000,10019988,10048911,10019994,10048911,10020003,10020000,10019988,10019986,10019994,10019986,10020003,10020001,10019988,10019986,10019994,10019986,10020003,10020001,10019988,10019986,10019994,10019986,10020003,10020001,10019988,10019986,10020002,10019986,10020003,10020005,10019988,10019986,10020002,10019986,10020003,10020005,10019988,10019987,10020002,10019987,10020004,10019988,10019987,10020002,10019987,10020004,10019988,10019987,10020002,10019987,10020004,10019988,10019987,10020002,10019987,10020004,10019989,10019999,10020004,10019989,10019999,10020004,10019989,10019999,10020004,10019989,10019999,10020004,10019989,10019999,10020004,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019989,10019999,10019999,10019999,10019999,10019999,10019999,10019999,10019999</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L24 W24/25; N=192; EHP=26874.000000; air:2x5,air:11x5,air:12x4,air:13x5,air:14x4,normal:17x23,normal:18x23,fast:30x6,heavy:31x2,heavy:40x2,fast:58x6,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x3,medium:83x10,swarm:84x53,heavy:86x3,heavy:88x3,fast:98x6,medium:108x9,medium:123x9,heavy:127x2</t>
+          <t>L24 W24/25; N=192; EHP=73221.833707; air:2x10,air:11x10,air:12x8,air:13x10,air:14x8,fast:30x6,fast:58x6,fast:64x5,fast:98x6,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x3,heavy:86x3,heavy:88x3,heavy:127x2,medium:83x10,medium:108x9,medium:123x9,normal:17x23,normal:18x23,swarm:84x30 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>10020009,10020020,10020011,10048912,10020019,10020012,10020027,10020009,10020020,10020011,10048912,10020019,10020012,10020009,10020020,10020011,10048912,10020019,10020012,10020009,10020020,10020011,10048912,10020019,10020013,10020009,10020020,10020011,10020006,10020019,10020013,10020009,10020020,10020014,10020006,10020019,10020016,10020009,10020020,10020014,10020006,10020019,10020016,10020009,10020020,10020014,10020006,10020019,10020017,10020009,10020020,10020014,10020006,10020019,10020017,10020009,10020020,10020014,10048913,10020024,10020018,10020009,10020020,10020014,10048913,10020024,10020018,10020009,10020020,10020015,10048913,10020024,10020018,10020009,10020020,10020015,10048913,10020024,10020021,10020009,10020020,10020015,10048913,10020024,10020021,10020009,10020020,10020015,10020007,10020024,10020021,10020009,10020020,10020015,10020007,10020024,10020022,10020009,10020020,10020015,10020007,10020024,10020022,10020009,10020020,10020023,10020007,10020024,10020026,10020009,10020020,10020023,10020007,10020024,10020026,10020009,10020020,10020023,10020008,10020025,10020009,10020020,10020023,10020008,10020025,10020009,10020020,10020023,10020008,10020025,10020009,10020020,10020023,10020008,10020025,10020009,10020020,10020008,10020025,10020010,10020020,10020025,10020010,10020020,10020025,10020010,10020020,10020025,10020010,10020020,10020025,10020010,10020020,10020025,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020020,10020020,10020020,10020020,10020020,10020020,10020020,10020020</t>
+          <t>10020009,10048912,10020011,10048912,10020019,10020012,10020027,10020009,10048912,10020011,10048912,10020019,10020012,10020009,10048912,10020011,10048912,10020019,10020012,10020009,10048912,10020011,10048912,10020019,10020013,10020009,10020006,10020011,10020006,10020019,10020013,10020009,10020006,10020014,10020006,10020019,10020016,10020009,10020006,10020014,10020006,10020019,10020016,10020009,10020006,10020014,10020006,10020019,10020017,10020009,10020006,10020014,10020006,10020019,10020017,10020009,10048913,10020014,10048913,10020024,10020018,10020009,10048913,10020014,10048913,10020024,10020018,10020009,10048913,10020015,10048913,10020024,10020018,10020009,10048913,10020015,10048913,10020024,10020021,10020009,10048913,10020015,10048913,10020024,10020021,10020009,10020007,10020015,10020007,10020024,10020021,10020009,10020007,10020015,10020007,10020024,10020022,10020009,10020007,10020015,10020007,10020024,10020022,10020009,10020007,10020023,10020007,10020024,10020026,10020009,10020007,10020023,10020007,10020024,10020026,10020009,10020008,10020023,10020008,10020025,10020009,10020008,10020023,10020008,10020025,10020009,10020008,10020023,10020008,10020025,10020009,10020008,10020023,10020008,10020025,10020009,10020008,10020008,10020025,10020010,10020020,10020025,10020010,10020020,10020025,10020010,10020020,10020025,10020010,10020020,10020025,10020010,10020020,10020025,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020010,10020020,10020020,10020020,10020020,10020020,10020020,10020020,10020020,10020020</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L24 W25/25; N=198; EHP=53636.000000; air:2x4,air:11x5,air:12x5,air:13x5,air:14x5,normal:17x24,normal:18x23,fast:30x5,heavy:31x3,heavy:40x2,fast:58x6,fast:64x6,heavy:67x2,heavy:70x2,heavy:80x3,medium:83x9,swarm:84x55,heavy:86x3,heavy:88x2,fast:98x6,medium:108x10,medium:123x10,heavy:127x2,boss:132x1</t>
+          <t>L24 W25/25; N=198; EHP=146132.423378; air:2x8,air:11x10,air:12x10,air:13x10,air:14x10,boss:132x1,fast:30x5,fast:58x6,fast:64x6,fast:98x6,heavy:31x3,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x3,heavy:86x3,heavy:88x2,heavy:127x2,medium:83x9,medium:108x10,medium:123x10,normal:17x24,normal:18x23,swarm:84x31 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L24/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L24/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>234</v>
+        <v>350</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>227</v>
+        <v>320</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>220</v>
+        <v>280</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>213</v>
+        <v>370</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>206</v>
+        <v>300</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>192</v>
+        <v>300</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>185</v>
+        <v>280</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>178</v>
+        <v>370</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>171</v>
+        <v>290</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>164</v>
+        <v>310</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>150</v>
+        <v>310</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>143</v>
+        <v>290</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>136</v>
+        <v>260</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>129</v>
+        <v>370</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>128</v>
+        <v>310</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>128</v>
+        <v>270</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>128</v>
+        <v>310</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>128</v>
+        <v>370</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>128</v>
+        <v>310</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>128</v>
+        <v>210</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
